--- a/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_EGY_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_EGY_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F28B8114-45D6-4753-B2DB-7A32C1110163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0BB84E52-CCC1-4243-AB06-E2ED117405B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -927,13 +927,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH04,S03aH02,S04aH06,S01aH03,S03aH03,S02aH02,S04aH05,S04aH08,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH06,S03aH05,S03aH08,S04aH07,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S04aH03,S04aH02,S01aH06,S02aH03</t>
+    <t>S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S01aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S04aH03,S04aH06,S04aH05,S04aH08,S02aH02,S03aH03,S04aH02,S03aH02,S01aH02,S04aH04,S02aH04,S02aH05</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH09,S04aH09,S04aH02,S02aH02,S04aH10,S03aH01,S03aH08,S03aH10,S01aH02,S03aH09,S01aH08,S02aH08,S04aH08,S01aH09,S02aH01,S02aH10,S01aH10,S03aH02,S01aH01,S04aH01</t>
+    <t>S01aH09,S01aH01,S04aH01,S03aH09,S01aH02,S02aH09,S04aH09,S02aH01,S02aH10,S03aH01,S02aH02,S04aH10,S04aH08,S01aH10,S03aH02,S04aH02,S01aH08,S02aH08,S03aH08,S03aH10</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH09,S04aH09,S04aH02,S02aH02,S04aH10,S03aH01,S03aH08,S03aH10,S01aH02,S03aH09,S01aH08,S02aH08,S04aH08,S01aH09,S02aH01,S02aH10,S01aH10,S03aH02,S01aH01,S04aH01</v>
+        <v>S01aH09,S01aH01,S04aH01,S03aH09,S01aH02,S02aH09,S04aH09,S02aH01,S02aH10,S03aH01,S02aH02,S04aH10,S04aH08,S01aH10,S03aH02,S04aH02,S01aH08,S02aH08,S03aH08,S03aH10</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH04,S03aH02,S04aH06,S01aH03,S03aH03,S02aH02,S04aH05,S04aH08,S02aH04,S02aH05,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S02aH06,S03aH05,S03aH08,S04aH07,S01aH02,S04aH04,S01aH04,S01aH07,S02aH07,S04aH03,S04aH02,S01aH06,S02aH03</v>
+        <v>S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S01aH03,S02aH06,S03aH05,S03aH08,S04aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S03aH04,S04aH03,S04aH06,S04aH05,S04aH08,S02aH02,S03aH03,S04aH02,S03aH02,S01aH02,S04aH04,S02aH04,S02aH05</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1656,7 +1656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19FD13FB-0B59-40AF-91A9-1FB7BC9D3D8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82A6E06D-265C-4988-9505-680A1E14C940}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1794,7 +1794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14691895-8E0B-4058-867C-FD87EC57A085}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B12C6DF-B22D-4026-8441-872EFF8BE581}">
   <dimension ref="B9:O1570"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -48656,7 +48656,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C93FFC2D-A811-45E5-8FB7-A2D1FA23FBA1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E2975B-D1DE-4280-B59E-E37F36250CB8}">
   <dimension ref="B9:FT101"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -73892,7 +73892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6315AB5-FDC7-4E96-9487-B68D66253344}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{814B5D83-C028-4455-BB75-98C23BC418EE}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -74482,7 +74482,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7923D9B2-706D-4BDF-A23D-A32242525860}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C936CD4-C554-48B2-86B1-D9DF0AA367AD}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -75389,7 +75389,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFD35299-1290-4ACB-B81B-DFFAFB02505F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FEEA6A-4A0F-447F-93F7-B43CF62E34D7}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -75856,7 +75856,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6BED46-C5F9-48D2-B391-9DCA6E3BF953}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E69DCB21-E0FE-46C4-AFBE-B0167999DBAD}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -75916,7 +75916,7 @@
         <v>43</v>
       </c>
       <c r="D13">
-        <v>0.86606666666666665</v>
+        <v>0.86606666666666676</v>
       </c>
       <c r="E13" t="s">
         <v>303</v>
@@ -75958,7 +75958,7 @@
         <v>41</v>
       </c>
       <c r="D16">
-        <v>0.65400000000000003</v>
+        <v>0.65399999999999991</v>
       </c>
       <c r="E16" t="s">
         <v>303</v>
@@ -75972,7 +75972,7 @@
         <v>43</v>
       </c>
       <c r="D17">
-        <v>0.84803333333333342</v>
+        <v>0.84803333333333331</v>
       </c>
       <c r="E17" t="s">
         <v>303</v>
@@ -76000,7 +76000,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.41543333333333338</v>
+        <v>0.41543333333333332</v>
       </c>
       <c r="E19" t="s">
         <v>303</v>
@@ -76056,7 +76056,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.43816666666666659</v>
+        <v>0.43816666666666665</v>
       </c>
       <c r="E23" t="s">
         <v>303</v>
@@ -76238,7 +76238,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.67540000000000011</v>
+        <v>0.67539999999999989</v>
       </c>
       <c r="E36" t="s">
         <v>303</v>
@@ -76252,7 +76252,7 @@
         <v>43</v>
       </c>
       <c r="D37">
-        <v>0.78216666666666657</v>
+        <v>0.78216666666666679</v>
       </c>
       <c r="E37" t="s">
         <v>303</v>
@@ -76308,7 +76308,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>0.7636666666666666</v>
+        <v>0.76366666666666683</v>
       </c>
       <c r="E41" t="s">
         <v>303</v>
@@ -76350,7 +76350,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.61099999999999999</v>
+        <v>0.6110000000000001</v>
       </c>
       <c r="E44" t="s">
         <v>303</v>
@@ -76392,7 +76392,7 @@
         <v>37</v>
       </c>
       <c r="D47">
-        <v>0.37470000000000003</v>
+        <v>0.37469999999999998</v>
       </c>
       <c r="E47" t="s">
         <v>303</v>
@@ -76434,7 +76434,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.47023333333333334</v>
+        <v>0.47023333333333328</v>
       </c>
       <c r="E50" t="s">
         <v>303</v>
@@ -76490,7 +76490,7 @@
         <v>45</v>
       </c>
       <c r="D54">
-        <v>0.45976666666666671</v>
+        <v>0.45976666666666666</v>
       </c>
       <c r="E54" t="s">
         <v>303</v>
@@ -76574,7 +76574,7 @@
         <v>41</v>
       </c>
       <c r="D60">
-        <v>0.71106666666666662</v>
+        <v>0.71106666666666651</v>
       </c>
       <c r="E60" t="s">
         <v>303</v>
@@ -76616,7 +76616,7 @@
         <v>37</v>
       </c>
       <c r="D63">
-        <v>0.39483333333333337</v>
+        <v>0.39483333333333331</v>
       </c>
       <c r="E63" t="s">
         <v>303</v>
@@ -76728,7 +76728,7 @@
         <v>37</v>
       </c>
       <c r="D71">
-        <v>0.42169999999999996</v>
+        <v>0.42170000000000002</v>
       </c>
       <c r="E71" t="s">
         <v>303</v>
@@ -76756,7 +76756,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.8026333333333332</v>
+        <v>0.80263333333333342</v>
       </c>
       <c r="E73" t="s">
         <v>303</v>
@@ -76840,7 +76840,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.4020333333333333</v>
+        <v>0.40203333333333341</v>
       </c>
       <c r="E79" t="s">
         <v>303</v>
@@ -77008,7 +77008,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.37656666666666666</v>
+        <v>0.37656666666666672</v>
       </c>
       <c r="E91" t="s">
         <v>303</v>
@@ -77036,7 +77036,7 @@
         <v>43</v>
       </c>
       <c r="D93">
-        <v>0.71476666666666677</v>
+        <v>0.71476666666666666</v>
       </c>
       <c r="E93" t="s">
         <v>303</v>
@@ -77050,7 +77050,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.51473333333333327</v>
+        <v>0.51473333333333338</v>
       </c>
       <c r="E94" t="s">
         <v>303</v>
@@ -77078,7 +77078,7 @@
         <v>41</v>
       </c>
       <c r="D96">
-        <v>0.54996666666666671</v>
+        <v>0.5499666666666666</v>
       </c>
       <c r="E96" t="s">
         <v>303</v>
@@ -77120,7 +77120,7 @@
         <v>37</v>
       </c>
       <c r="D99">
-        <v>0.3666666666666667</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="E99" t="s">
         <v>303</v>
@@ -77148,7 +77148,7 @@
         <v>43</v>
       </c>
       <c r="D101">
-        <v>0.72253333333333325</v>
+        <v>0.72253333333333336</v>
       </c>
       <c r="E101" t="s">
         <v>303</v>
@@ -77190,7 +77190,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.5986999999999999</v>
+        <v>0.59870000000000001</v>
       </c>
       <c r="E104" t="s">
         <v>303</v>
@@ -77428,7 +77428,7 @@
         <v>43</v>
       </c>
       <c r="D121">
-        <v>0.67903333333333327</v>
+        <v>0.67903333333333338</v>
       </c>
       <c r="E121" t="s">
         <v>303</v>
